--- a/output/Tables/Best practice/prop_below_target.xlsx
+++ b/output/Tables/Best practice/prop_below_target.xlsx
@@ -383,13 +383,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>71.26045803419986</v>
+        <v>73.40214204598983</v>
       </c>
       <c r="C2">
-        <v>69.3308096391858</v>
+        <v>71.50260023584877</v>
       </c>
       <c r="D2">
-        <v>73.19010642921391</v>
+        <v>75.30168385613089</v>
       </c>
     </row>
     <row r="3">
@@ -399,13 +399,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>70.78370479040366</v>
+        <v>73.86226442315072</v>
       </c>
       <c r="C3">
-        <v>69.12129579615528</v>
+        <v>72.26635324425447</v>
       </c>
       <c r="D3">
-        <v>72.44611378465206</v>
+        <v>75.45817560204695</v>
       </c>
     </row>
     <row r="4">
@@ -415,13 +415,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>51.53434166973542</v>
+        <v>54.66542384971016</v>
       </c>
       <c r="C4">
-        <v>49.7505533640963</v>
+        <v>52.88909387827906</v>
       </c>
       <c r="D4">
-        <v>53.31812997537454</v>
+        <v>56.44175382114126</v>
       </c>
     </row>
   </sheetData>
